--- a/data/trans_orig/IP13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP13-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>20839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124974</t>
+          <t>124871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134466</t>
+          <t>134593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141725</t>
+          <t>141928</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150115</t>
+          <t>150101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271389</t>
+          <t>270964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>283469</t>
+          <t>283234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16035</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179063</t>
+          <t>178702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188988</t>
+          <t>189037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192749</t>
+          <t>193921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204209</t>
+          <t>204694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376249</t>
+          <t>376243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>391270</t>
+          <t>391097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123636</t>
+          <t>123407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132766</t>
+          <t>132325</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136574</t>
+          <t>136518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145327</t>
+          <t>145201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264331</t>
+          <t>263243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276241</t>
+          <t>276123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20694</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>201336</t>
+          <t>201086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208523</t>
+          <t>207889</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192422</t>
+          <t>192591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202485</t>
+          <t>202976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396445</t>
+          <t>397221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>408834</t>
+          <t>408250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44952</t>
+          <t>45549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>54060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81258</t>
+          <t>80167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>641158</t>
+          <t>641694</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>657870</t>
+          <t>658371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>677748</t>
+          <t>677151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>695220</t>
+          <t>695515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1322463</t>
+          <t>1323554</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1349325</t>
+          <t>1349661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23518</t>
+          <t>24205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124588</t>
+          <t>123698</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135084</t>
+          <t>134731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140957</t>
+          <t>141402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150013</t>
+          <t>149905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>269522</t>
+          <t>268835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>282988</t>
+          <t>283255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>33461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185663</t>
+          <t>185901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196823</t>
+          <t>196739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204947</t>
+          <t>204889</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216496</t>
+          <t>216783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395352</t>
+          <t>395523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411138</t>
+          <t>411902</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>13340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22297</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>30518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142918</t>
+          <t>142036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151374</t>
+          <t>151814</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142867</t>
+          <t>142975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154860</t>
+          <t>154433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>288892</t>
+          <t>290022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>304058</t>
+          <t>304907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29913</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195008</t>
+          <t>195140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205161</t>
+          <t>205012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188749</t>
+          <t>188306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>200755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>388138</t>
+          <t>387897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>404205</t>
+          <t>403554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29857</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49742</t>
+          <t>50555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>36046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57807</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>71740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100565</t>
+          <t>101689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>660440</t>
+          <t>659627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>681251</t>
+          <t>680325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>692626</t>
+          <t>692099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>714582</t>
+          <t>714387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1360050</t>
+          <t>1358926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1389347</t>
+          <t>1388875</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14889</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125539</t>
+          <t>124816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132270</t>
+          <t>132222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137641</t>
+          <t>137942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146101</t>
+          <t>146140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266894</t>
+          <t>266527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277278</t>
+          <t>277237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>32420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189132</t>
+          <t>188807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199892</t>
+          <t>199303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>205901</t>
+          <t>206537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217178</t>
+          <t>217025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>398795</t>
+          <t>399186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>414028</t>
+          <t>414183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>16069</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>27225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140490</t>
+          <t>139928</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150307</t>
+          <t>149902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150258</t>
+          <t>150008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160758</t>
+          <t>160462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>294368</t>
+          <t>295445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308979</t>
+          <t>308718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18202</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189218</t>
+          <t>189264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201131</t>
+          <t>200963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194886</t>
+          <t>193736</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202889</t>
+          <t>202582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386904</t>
+          <t>388139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401398</t>
+          <t>401862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>28561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47522</t>
+          <t>47171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44007</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57121</t>
+          <t>57615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83544</t>
+          <t>83620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>657200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>675904</t>
+          <t>675810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>700837</t>
+          <t>701725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720231</t>
+          <t>720800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1365671</t>
+          <t>1365595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1392094</t>
+          <t>1391600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107798</t>
+          <t>107679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115045</t>
+          <t>115001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128259</t>
+          <t>128153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136734</t>
+          <t>136999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>239355</t>
+          <t>238562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250421</t>
+          <t>250290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174078</t>
+          <t>173767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184086</t>
+          <t>184243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>234154</t>
+          <t>233799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246457</t>
+          <t>246810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>412434</t>
+          <t>413199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>428530</t>
+          <t>428256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21570</t>
+          <t>22264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35467</t>
+          <t>36859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171093</t>
+          <t>170993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183871</t>
+          <t>183800</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163716</t>
+          <t>163022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176499</t>
+          <t>176587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339404</t>
+          <t>338012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357515</t>
+          <t>356919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22359</t>
+          <t>22232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34188</t>
+          <t>34131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151531</t>
+          <t>151025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162113</t>
+          <t>161725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158879</t>
+          <t>159006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172320</t>
+          <t>172009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315013</t>
+          <t>315070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331418</t>
+          <t>331773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48293</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71310</t>
+          <t>71550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102119</t>
+          <t>102444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>617047</t>
+          <t>618104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>637527</t>
+          <t>637340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>701590</t>
+          <t>699766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>724706</t>
+          <t>723830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1324469</t>
+          <t>1324144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1355278</t>
+          <t>1355038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP13-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6047</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10665</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7619</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4133</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13855</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4045</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13137</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6047</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2976</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11149</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>20793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>147030</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>142412</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>149924</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131107</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>124871</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>134593</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>125589</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>134681</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>147030</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141928</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,05%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>270964</t>
+          <t>271010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>283234</t>
+          <t>282816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12638</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7946</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18756</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9958</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6126</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16461</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6134</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15628</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,1%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>3,14%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12638</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7448</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18221</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>30279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>199504</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>193386</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>204196</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>185205</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>178702</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>189037</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>179535</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>189029</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,9%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>96,86%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>199504</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>193921</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>204694</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>599</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376243</t>
+          <t>377026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>391097</t>
+          <t>391920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7931</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4287</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12806</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9087</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5492</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14410</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5440</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14741</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7931</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13139</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24231</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141726</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>136851</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145370</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>128730</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>123407</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>132325</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>123076</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>132377</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141726</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>136518</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>145201</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263243</t>
+          <t>262285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276123</t>
+          <t>276130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9514</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5456</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15520</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3747</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8229</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8343</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9514</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4848</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15233</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>198310</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>192304</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202368</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205568</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>201086</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>207889</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>200972</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>207851</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>198310</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>192591</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202976</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>397221</t>
+          <t>397050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>408250</t>
+          <t>408805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36130</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27358</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46481</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>30410</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22650</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>39327</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21917</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>39561</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>36130</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27185</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>45549</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54060</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80167</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>686570</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>676219</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>695342</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>650611</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>641694</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>658371</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>641460</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>659104</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>686570</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>677151</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>695515</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1323554</t>
+          <t>1324821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1349661</t>
+          <t>1349824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7347</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13097</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8756</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4626</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15659</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4331</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15267</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7347</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3778</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12281</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24205</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>146336</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>140586</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>149859</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>130601</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>123698</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>134731</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>124090</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>135026</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>146336</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141402</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>149905</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,22%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>268835</t>
+          <t>268895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>283255</t>
+          <t>282880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153683</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153683</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153683</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11858</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19014</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13041</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8410</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19248</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19964</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11858</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7052</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18946</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>33187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>204821</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>216787</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>192108</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>185901</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>196739</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>185185</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>196649</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>211977</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>204889</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>216783</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395523</t>
+          <t>395797</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411902</t>
+          <t>411178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205149</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205149</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205149</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15268</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10156</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22483</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7456</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3562</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13340</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12548</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15268</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10731</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22189</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30518</t>
+          <t>31223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -3474,67 +3474,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>149896</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142681</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>155008</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>142036</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>151814</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>142828</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>151483</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149896</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>142975</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>154433</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290022</t>
+          <t>289317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>304907</t>
+          <t>304153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165164</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165164</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165164</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165164</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165164</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165164</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11627</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6708</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18224</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9368</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15160</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5093</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15534</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11627</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6996</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19445</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30154</t>
+          <t>29546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>196124</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>189527</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201043</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200932</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>195140</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>205012</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>194766</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>205207</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>196124</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>188306</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>200755</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,4%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>387897</t>
+          <t>388505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403554</t>
+          <t>404036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207751</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207751</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207751</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207751</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207751</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207751</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,107 +4042,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46100</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36103</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>57724</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38621</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29857</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50555</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29760</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50695</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>46100</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>36046</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>58334</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>84722</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>70068</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>100074</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>84722</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>71740</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>101689</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -4155,107 +4155,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>704333</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>692709</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>714330</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>968</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>671561</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>659627</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>680325</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>659487</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>680422</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,56%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>704333</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>692099</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>714387</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1375893</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1360541</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1390547</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>95,2%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1375893</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1358926</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1388875</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>750433</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>750433</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>750433</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710182</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710182</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710182</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>750433</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>750433</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>750433</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4622,67 +4622,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>4774</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10266</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>4046</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8891</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7920</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4774</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10134</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15256</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>143302</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>137810</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>146073</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>129661</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>124816</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>132222</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>125787</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>132312</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,97%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>143302</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>137942</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>146140</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266527</t>
+          <t>266775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277237</t>
+          <t>277060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11602</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18135</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12175</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7944</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18440</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7853</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18344</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11602</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7334</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17822</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>31478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212757</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>206224</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>217649</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>195072</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>188807</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>199303</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>188903</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>199394</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>212757</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>206537</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>217025</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,83%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>399186</t>
+          <t>400128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>414183</t>
+          <t>415132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10247</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5811</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16187</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9779</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6095</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16069</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5971</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15236</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10247</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6211</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16665</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27225</t>
+          <t>27991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156426</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>150486</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>160862</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>146218</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>139928</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149902</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>140761</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>150026</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,73%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>156426</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>150008</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>160462</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295445</t>
+          <t>294679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308718</t>
+          <t>308712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6263</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11690</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11064</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6457</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18156</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6681</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17212</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6263</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3154</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>199473</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>194046</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202702</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>196356</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>189264</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>200963</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>190208</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>200739</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>199473</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>193736</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202582</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>388139</t>
+          <t>387723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401862</t>
+          <t>402019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32886</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24341</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43080</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>37065</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28561</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47171</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28392</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>46841</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>32886</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>24044</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>43119</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>58617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83620</t>
+          <t>86489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>711958</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>701764</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>720503</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>667306</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>657200</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>675810</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>657530</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>675979</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>711958</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>701725</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>720800</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1365595</t>
+          <t>1362726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1391600</t>
+          <t>1390598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>119490</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>113513</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>122541</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>112017</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>107679</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>115001</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>133707</t>
+          <t>115580</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128153</t>
+          <t>110381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136999</t>
+          <t>118576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>245724</t>
+          <t>235071</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238562</t>
+          <t>228421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250290</t>
+          <t>239429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256969</t>
+          <t>246441</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256969</t>
+          <t>246441</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256969</t>
+          <t>246441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13198</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8356</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20277</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10520</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6269</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16745</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17292</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32349</t>
+          <t>32700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>224008</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>216929</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>228850</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>179992</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>173767</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184243</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>241532</t>
+          <t>174803</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233799</t>
+          <t>168987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246810</t>
+          <t>178520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>421525</t>
+          <t>398811</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>413199</t>
+          <t>388919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>428256</t>
+          <t>405500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12745</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7599</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11643</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5785</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18592</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>24823</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>17533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36859</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155596</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>147562</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>160742</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>177942</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>170993</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>183800</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>171165</t>
+          <t>144126</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163022</t>
+          <t>135999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176587</t>
+          <t>148929</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>299722</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>338012</t>
+          <t>290331</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>356919</t>
+          <t>307012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13811</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8942</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20783</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10011</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6237</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16937</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,22 +7668,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>32410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>155565</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148593</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>160434</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>157951</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>151025</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161725</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>166427</t>
+          <t>157547</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159006</t>
+          <t>151463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172009</t>
+          <t>161618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>324379</t>
+          <t>313113</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315070</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331773</t>
+          <t>319728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45633</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35761</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>58317</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>37437</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47236</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48417</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>28041</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61482</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>85854</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71550</t>
+          <t>68193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102444</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>654660</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>641976</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>664532</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>884</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>627903</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>618104</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>637340</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>712831</t>
+          <t>592056</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>699766</t>
+          <t>581075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>723830</t>
+          <t>600792</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1340734</t>
+          <t>1246716</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1324144</t>
+          <t>1229241</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1355038</t>
+          <t>1260932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
